--- a/output/pdf_financials_xlsx/MGM.xlsx
+++ b/output/pdf_financials_xlsx/MGM.xlsx
@@ -1060,31 +1060,31 @@
         <v>-1.028827</v>
       </c>
       <c r="E16" s="3" t="n">
-        <v>3.025625</v>
+        <v>-3.025625</v>
       </c>
       <c r="F16" s="3" t="n">
-        <v>12.297067</v>
+        <v>-12.297067</v>
       </c>
       <c r="G16" s="3" t="n">
-        <v>5.681912</v>
+        <v>-5.681912</v>
       </c>
       <c r="H16" s="3" t="n">
-        <v>5.681912</v>
+        <v>-5.681912</v>
       </c>
       <c r="I16" s="3" t="n">
-        <v>5.933298</v>
+        <v>-5.933298</v>
       </c>
       <c r="J16" s="3" t="n">
-        <v>10.279928</v>
+        <v>-10.279928</v>
       </c>
       <c r="K16" s="3" t="n">
-        <v>7.032138</v>
+        <v>-7.032138</v>
       </c>
       <c r="L16" s="3" t="n">
-        <v>4.444315</v>
+        <v>-4.444315</v>
       </c>
       <c r="M16" s="3" t="n">
-        <v>8.185131999999999</v>
+        <v>-8.185131999999999</v>
       </c>
     </row>
     <row r="17">
@@ -1280,31 +1280,31 @@
         <v>-1.028827</v>
       </c>
       <c r="E20" s="3" t="n">
-        <v>3.025625</v>
+        <v>-3.025625</v>
       </c>
       <c r="F20" s="3" t="n">
-        <v>12.297067</v>
+        <v>-12.297067</v>
       </c>
       <c r="G20" s="3" t="n">
-        <v>5.681912</v>
+        <v>-5.681912</v>
       </c>
       <c r="H20" s="3" t="n">
-        <v>5.681912</v>
+        <v>-5.681912</v>
       </c>
       <c r="I20" s="3" t="n">
-        <v>5.933298</v>
+        <v>-5.933298</v>
       </c>
       <c r="J20" s="3" t="n">
-        <v>10.279928</v>
+        <v>-10.279928</v>
       </c>
       <c r="K20" s="3" t="n">
-        <v>7.032138</v>
+        <v>-7.032138</v>
       </c>
       <c r="L20" s="3" t="n">
-        <v>4.444315</v>
+        <v>-4.444315</v>
       </c>
       <c r="M20" s="3" t="n">
-        <v>8.185131999999999</v>
+        <v>-8.185131999999999</v>
       </c>
     </row>
     <row r="21">
@@ -1409,31 +1409,31 @@
         <v>-1.028827</v>
       </c>
       <c r="E23" s="3" t="n">
-        <v>3.025625</v>
+        <v>-3.025625</v>
       </c>
       <c r="F23" s="3" t="n">
-        <v>12.297067</v>
+        <v>-12.297067</v>
       </c>
       <c r="G23" s="3" t="n">
-        <v>5.681912</v>
+        <v>-5.681912</v>
       </c>
       <c r="H23" s="3" t="n">
-        <v>5.681912</v>
+        <v>-5.681912</v>
       </c>
       <c r="I23" s="3" t="n">
-        <v>5.933298</v>
+        <v>-5.933298</v>
       </c>
       <c r="J23" s="3" t="n">
-        <v>10.279928</v>
+        <v>-10.279928</v>
       </c>
       <c r="K23" s="3" t="n">
-        <v>7.032138</v>
+        <v>-7.032138</v>
       </c>
       <c r="L23" s="3" t="n">
-        <v>4.444315</v>
+        <v>-4.444315</v>
       </c>
       <c r="M23" s="3" t="n">
-        <v>8.185131999999999</v>
+        <v>-8.185131999999999</v>
       </c>
     </row>
     <row r="24">
@@ -1560,13 +1560,13 @@
         </is>
       </c>
       <c r="E26" s="3" t="n">
-        <v>75.640625</v>
+        <v>-75.640625</v>
       </c>
       <c r="F26" s="3" t="n">
-        <v>153.713338</v>
+        <v>-153.713338</v>
       </c>
       <c r="G26" s="3" t="n">
-        <v>189.397067</v>
+        <v>-189.397067</v>
       </c>
       <c r="H26" s="1" t="inlineStr">
         <is>
@@ -1574,19 +1574,19 @@
         </is>
       </c>
       <c r="I26" s="3" t="n">
-        <v>296.6649</v>
+        <v>-296.6649</v>
       </c>
       <c r="J26" s="3" t="n">
-        <v>342.664267</v>
+        <v>-342.664267</v>
       </c>
       <c r="K26" s="3" t="n">
-        <v>351.6069</v>
+        <v>-351.6069</v>
       </c>
       <c r="L26" s="3" t="n">
-        <v>37.035958</v>
+        <v>-37.035958</v>
       </c>
       <c r="M26" s="3" t="n">
-        <v>48.147835</v>
+        <v>-48.147835</v>
       </c>
     </row>
     <row r="27">
@@ -1605,31 +1605,31 @@
         <v>-1.032606</v>
       </c>
       <c r="E27" s="3" t="n">
-        <v>3.027029</v>
+        <v>-3.024221</v>
       </c>
       <c r="F27" s="3" t="n">
-        <v>12.328161</v>
+        <v>-12.265973</v>
       </c>
       <c r="G27" s="3" t="n">
-        <v>5.777956</v>
+        <v>-5.585868</v>
       </c>
       <c r="H27" s="3" t="n">
-        <v>5.681912</v>
+        <v>-5.681912</v>
       </c>
       <c r="I27" s="3" t="n">
-        <v>5.933298</v>
+        <v>-5.933298</v>
       </c>
       <c r="J27" s="3" t="n">
-        <v>10.279928</v>
+        <v>-10.279928</v>
       </c>
       <c r="K27" s="3" t="n">
-        <v>7.958314</v>
+        <v>-6.105962</v>
       </c>
       <c r="L27" s="3" t="n">
-        <v>5.426331</v>
+        <v>-3.462299</v>
       </c>
       <c r="M27" s="3" t="n">
-        <v>8.386616999999999</v>
+        <v>-7.983647</v>
       </c>
     </row>
     <row r="28">
@@ -1691,31 +1691,31 @@
         <v>-1.032606</v>
       </c>
       <c r="E29" s="3" t="n">
-        <v>3.027029</v>
+        <v>-3.024221</v>
       </c>
       <c r="F29" s="3" t="n">
-        <v>12.328161</v>
+        <v>-12.265973</v>
       </c>
       <c r="G29" s="3" t="n">
-        <v>5.777956</v>
+        <v>-5.585868</v>
       </c>
       <c r="H29" s="3" t="n">
-        <v>5.771136</v>
+        <v>-5.592688</v>
       </c>
       <c r="I29" s="3" t="n">
-        <v>6.237564</v>
+        <v>-5.629032</v>
       </c>
       <c r="J29" s="3" t="n">
-        <v>10.492847</v>
+        <v>-10.067009</v>
       </c>
       <c r="K29" s="3" t="n">
-        <v>8.177424</v>
+        <v>-5.886852</v>
       </c>
       <c r="L29" s="3" t="n">
-        <v>5.613403</v>
+        <v>-3.275227</v>
       </c>
       <c r="M29" s="3" t="n">
-        <v>8.553494000000001</v>
+        <v>-7.81677</v>
       </c>
     </row>
     <row r="30">
@@ -1801,31 +1801,31 @@
         <v>-0</v>
       </c>
       <c r="E31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="F31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="G31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="H31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="I31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="J31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="K31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="L31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
       <c r="M31" s="3" t="n">
-        <v>0</v>
+        <v>-0</v>
       </c>
     </row>
     <row r="32">
@@ -4447,40 +4447,40 @@
         </is>
       </c>
       <c r="B92" s="3" t="n">
-        <v>0</v>
+        <v>1.628976</v>
       </c>
       <c r="C92" s="3" t="n">
-        <v>0</v>
+        <v>1.628976</v>
       </c>
       <c r="D92" s="3" t="n">
-        <v>0</v>
+        <v>0.912567</v>
       </c>
       <c r="E92" s="3" t="n">
-        <v>0</v>
+        <v>5.473029</v>
       </c>
       <c r="F92" s="3" t="n">
-        <v>0</v>
+        <v>10.732663</v>
       </c>
       <c r="G92" s="3" t="n">
-        <v>0</v>
+        <v>11.022877</v>
       </c>
       <c r="H92" s="3" t="n">
-        <v>0</v>
+        <v>11.398483</v>
       </c>
       <c r="I92" s="3" t="n">
-        <v>0</v>
+        <v>14.392629</v>
       </c>
       <c r="J92" s="3" t="n">
-        <v>0</v>
+        <v>15.541566</v>
       </c>
       <c r="K92" s="3" t="n">
-        <v>0</v>
+        <v>15.855538</v>
       </c>
       <c r="L92" s="3" t="n">
-        <v>0</v>
+        <v>16.230879</v>
       </c>
       <c r="M92" s="3" t="n">
-        <v>0</v>
+        <v>16.230879</v>
       </c>
     </row>
     <row r="93">
@@ -4736,7 +4736,7 @@
         <v>-5.681912</v>
       </c>
       <c r="H99" s="3" t="n">
-        <v>5.681912</v>
+        <v>-5.681912</v>
       </c>
       <c r="I99" s="3" t="n">
         <v>-5.933298</v>
@@ -8092,7 +8092,11 @@
           <t>Reserves 17,432,554</t>
         </is>
       </c>
-      <c r="D24" t="inlineStr"/>
+      <c r="D24" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E24" t="inlineStr">
         <is>
           <t>-</t>
@@ -9702,7 +9706,11 @@
           <t>Reserves 13</t>
         </is>
       </c>
-      <c r="D46" t="inlineStr"/>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E46" t="inlineStr">
         <is>
           <t>-</t>
@@ -10592,7 +10600,11 @@
           <t>Reserves 12</t>
         </is>
       </c>
-      <c r="D58" t="inlineStr"/>
+      <c r="D58" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E58" t="inlineStr">
         <is>
           <t>-</t>
@@ -11408,7 +11420,11 @@
           <t>Reserves 11</t>
         </is>
       </c>
-      <c r="D69" t="inlineStr"/>
+      <c r="D69" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E69" t="inlineStr">
         <is>
           <t>-</t>
@@ -12296,7 +12312,11 @@
           <t>Reserves 10</t>
         </is>
       </c>
-      <c r="D81" t="inlineStr"/>
+      <c r="D81" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E81" t="inlineStr">
         <is>
           <t>-</t>
@@ -12586,7 +12606,11 @@
           <t>Reserves 9</t>
         </is>
       </c>
-      <c r="D85" t="inlineStr"/>
+      <c r="D85" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E85" t="inlineStr">
         <is>
           <t>-</t>
@@ -13782,7 +13806,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D101" t="inlineStr"/>
+      <c r="D101" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E101" t="inlineStr">
         <is>
           <t>-</t>
@@ -15244,7 +15272,11 @@
           <t>Reserves 912,567</t>
         </is>
       </c>
-      <c r="D120" t="inlineStr"/>
+      <c r="D120" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E120" t="inlineStr">
         <is>
           <t>-</t>
@@ -16304,7 +16336,11 @@
           <t>Reserves</t>
         </is>
       </c>
-      <c r="D134" t="inlineStr"/>
+      <c r="D134" t="inlineStr">
+        <is>
+          <t>AdditionalPaidInCapital</t>
+        </is>
+      </c>
       <c r="E134" s="5" t="n">
         <v>1.628976</v>
       </c>
@@ -26039,19 +26075,19 @@
         </is>
       </c>
       <c r="L265" s="5" t="n">
-        <v>5.933298</v>
+        <v>-5.933298</v>
       </c>
       <c r="M265" s="5" t="n">
-        <v>10.279928</v>
+        <v>-10.279928</v>
       </c>
       <c r="N265" s="5" t="n">
-        <v>7.032138</v>
+        <v>-7.032138</v>
       </c>
       <c r="O265" s="5" t="n">
-        <v>4.444315</v>
+        <v>-4.444315</v>
       </c>
       <c r="P265" s="5" t="n">
-        <v>8.185131999999999</v>
+        <v>-8.185131999999999</v>
       </c>
     </row>
     <row r="266">
@@ -28650,7 +28686,7 @@
         </is>
       </c>
       <c r="K300" s="5" t="n">
-        <v>5.681912</v>
+        <v>-5.681912</v>
       </c>
       <c r="L300" t="inlineStr">
         <is>
@@ -29171,13 +29207,13 @@
         </is>
       </c>
       <c r="H307" s="5" t="n">
-        <v>3.025625</v>
+        <v>-3.025625</v>
       </c>
       <c r="I307" s="5" t="n">
-        <v>12.297067</v>
+        <v>-12.297067</v>
       </c>
       <c r="J307" s="5" t="n">
-        <v>5.681912</v>
+        <v>-5.681912</v>
       </c>
       <c r="K307" t="inlineStr">
         <is>
@@ -29328,10 +29364,10 @@
         </is>
       </c>
       <c r="I309" s="5" t="n">
-        <v>12.088149</v>
+        <v>-12.088149</v>
       </c>
       <c r="J309" s="5" t="n">
-        <v>5.681912</v>
+        <v>-5.681912</v>
       </c>
       <c r="K309" t="inlineStr">
         <is>
@@ -30009,10 +30045,10 @@
         </is>
       </c>
       <c r="H318" s="5" t="n">
-        <v>2.960825</v>
+        <v>-2.960825</v>
       </c>
       <c r="I318" s="5" t="n">
-        <v>12.088149</v>
+        <v>-12.088149</v>
       </c>
       <c r="J318" t="inlineStr">
         <is>
@@ -31283,7 +31319,7 @@
         <v>-0.0324</v>
       </c>
       <c r="H335" s="5" t="n">
-        <v>0.0648</v>
+        <v>-0.0648</v>
       </c>
       <c r="I335" t="inlineStr">
         <is>

--- a/output/pdf_financials_xlsx/MGM.xlsx
+++ b/output/pdf_financials_xlsx/MGM.xlsx
@@ -5298,13 +5298,13 @@
         <v>0</v>
       </c>
       <c r="I112" s="3" t="n">
-        <v>0</v>
+        <v>0.045</v>
       </c>
       <c r="J112" s="3" t="n">
         <v>0</v>
       </c>
       <c r="K112" s="3" t="n">
-        <v>0</v>
+        <v>0.0155</v>
       </c>
       <c r="L112" s="3" t="n">
         <v>0</v>
@@ -18710,7 +18710,11 @@
           <t>Loss on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D168" t="inlineStr"/>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E168" t="inlineStr">
         <is>
           <t>-</t>
@@ -19078,7 +19082,11 @@
           <t>Proceeds on disposal of property and equipment</t>
         </is>
       </c>
-      <c r="D173" t="inlineStr"/>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E173" t="inlineStr">
         <is>
           <t>-</t>
@@ -21194,7 +21202,11 @@
           <t>Proceeds on sale of property and equipment 16,546</t>
         </is>
       </c>
-      <c r="D201" t="inlineStr"/>
+      <c r="D201" t="inlineStr">
+        <is>
+          <t>SaleOfPPE</t>
+        </is>
+      </c>
       <c r="E201" t="inlineStr">
         <is>
           <t>-</t>

--- a/output/pdf_financials_xlsx/MGM.xlsx
+++ b/output/pdf_financials_xlsx/MGM.xlsx
@@ -3502,10 +3502,10 @@
         <v>0</v>
       </c>
       <c r="I70" s="3" t="n">
-        <v>0</v>
+        <v>0.194985</v>
       </c>
       <c r="J70" s="3" t="n">
-        <v>0</v>
+        <v>0.160668</v>
       </c>
       <c r="K70" s="3" t="n">
         <v>0</v>
@@ -3545,10 +3545,10 @@
         <v>0</v>
       </c>
       <c r="I71" s="3" t="n">
-        <v>0.04</v>
+        <v>0.234985</v>
       </c>
       <c r="J71" s="3" t="n">
-        <v>0.04</v>
+        <v>0.200668</v>
       </c>
       <c r="K71" s="3" t="n">
         <v>0.04</v>
@@ -3717,10 +3717,10 @@
         <v>1.650397</v>
       </c>
       <c r="I75" s="3" t="n">
-        <v>3.302124</v>
+        <v>3.107139</v>
       </c>
       <c r="J75" s="3" t="n">
-        <v>0.744578</v>
+        <v>0.58391</v>
       </c>
       <c r="K75" s="3" t="n">
         <v>0.778002</v>
@@ -3946,10 +3946,10 @@
         </is>
       </c>
       <c r="I80" s="3" t="n">
-        <v>0.002234683562662147</v>
+        <v>0.01312792792430412</v>
       </c>
       <c r="J80" s="3" t="n">
-        <v>0.03401084810429039</v>
+        <v>0.05128036458298064</v>
       </c>
       <c r="K80" s="3" t="n">
         <v>0.0347241390695678</v>
@@ -5418,7 +5418,7 @@
         <v>0</v>
       </c>
       <c r="F115" s="3" t="n">
-        <v>0</v>
+        <v>0.215553</v>
       </c>
       <c r="G115" s="3" t="n">
         <v>0</v>
@@ -11044,7 +11044,11 @@
           <t>Lease liabilities 9</t>
         </is>
       </c>
-      <c r="D64" t="inlineStr"/>
+      <c r="D64" t="inlineStr">
+        <is>
+          <t>CurrentCapitalLeaseObligation</t>
+        </is>
+      </c>
       <c r="E64" t="inlineStr">
         <is>
           <t>-</t>
@@ -22736,7 +22740,11 @@
           <t>Proceeds on sale of marketable securities</t>
         </is>
       </c>
-      <c r="D221" t="inlineStr"/>
+      <c r="D221" t="inlineStr">
+        <is>
+          <t>SaleOfInvestment</t>
+        </is>
+      </c>
       <c r="E221" t="inlineStr">
         <is>
           <t>-</t>
